--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$65</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="102">
   <si>
     <t>设备名称</t>
   </si>
@@ -74,10 +74,7 @@
     <t>采集开始</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>1B22</t>
+    <t>B</t>
   </si>
   <si>
     <t>Boolean</t>
@@ -89,33 +86,39 @@
     <t>D</t>
   </si>
   <si>
+    <t>UInt16</t>
+  </si>
+  <si>
+    <t>整数</t>
+  </si>
+  <si>
+    <t>型号B</t>
+  </si>
+  <si>
+    <t>屏蔽工位B</t>
+  </si>
+  <si>
+    <t>Int32</t>
+  </si>
+  <si>
+    <t>sting</t>
+  </si>
+  <si>
+    <t>NG代码B</t>
+  </si>
+  <si>
     <t>Int16</t>
   </si>
   <si>
-    <t>整数</t>
-  </si>
-  <si>
-    <t>型号B</t>
-  </si>
-  <si>
-    <t>屏蔽工位B</t>
-  </si>
-  <si>
-    <t>Int32</t>
-  </si>
-  <si>
-    <t>sting</t>
-  </si>
-  <si>
-    <t>NG代码B</t>
-  </si>
-  <si>
     <t>A线托盘编号</t>
   </si>
   <si>
     <t>识别代码</t>
   </si>
   <si>
+    <t>UInt32</t>
+  </si>
+  <si>
     <t>正游隙检测值</t>
   </si>
   <si>
@@ -155,9 +158,18 @@
     <t>密封圈压装压力</t>
   </si>
   <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>kgf</t>
+  </si>
+  <si>
     <t>密封圈压装位移B</t>
   </si>
   <si>
+    <t>mm</t>
+  </si>
+  <si>
     <t>磁性圈平行差检测传感器1</t>
   </si>
   <si>
@@ -233,15 +245,15 @@
     <t>String</t>
   </si>
   <si>
-    <t>半成品码</t>
-  </si>
-  <si>
     <t>A线</t>
   </si>
   <si>
     <t>100.100.100.1</t>
   </si>
   <si>
+    <t>外法兰半成品码</t>
+  </si>
+  <si>
     <t>托盘号A</t>
   </si>
   <si>
@@ -251,15 +263,21 @@
     <t>屏蔽工位A</t>
   </si>
   <si>
-    <t>PASS</t>
+    <t>二进制</t>
+  </si>
+  <si>
+    <t>32位每位代表一个pass点</t>
+  </si>
+  <si>
+    <t>NG代码A</t>
+  </si>
+  <si>
+    <t>每个数字代表一个一个NG</t>
   </si>
   <si>
     <t>显示的是字符</t>
   </si>
   <si>
-    <t>NG代码A</t>
-  </si>
-  <si>
     <t>小内圈分选数据</t>
   </si>
   <si>
@@ -275,12 +293,21 @@
     <t>B面钢球组差</t>
   </si>
   <si>
+    <t>4B0</t>
+  </si>
+  <si>
     <t>A面钢球注脂量</t>
   </si>
   <si>
+    <t>g</t>
+  </si>
+  <si>
     <t>密封圈压装力</t>
   </si>
   <si>
+    <t>Kgf</t>
+  </si>
+  <si>
     <t>密封圈压装位移A</t>
   </si>
   <si>
@@ -306,6 +333,9 @@
   </si>
   <si>
     <t>小内圈合套位移</t>
+  </si>
+  <si>
+    <t>内法兰半成品码</t>
   </si>
 </sst>
 </file>
@@ -956,7 +986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -984,12 +1014,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1011,11 +1047,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1340,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1355,6 +1400,7 @@
     <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="11" max="11" width="12.625" style="4" customWidth="1"/>
     <col min="12" max="12" width="9" style="3"/>
+    <col min="14" max="14" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" spans="1:12">
@@ -1405,146 +1451,146 @@
       <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="8">
+        <v>599</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="10">
+        <v>1</v>
+      </c>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="9">
-        <v>1</v>
-      </c>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:12">
-      <c r="A3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="10">
+        <v>13000</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="9">
-        <v>13000</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>1</v>
       </c>
       <c r="J3" s="6"/>
       <c r="L3" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:12">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="10">
+        <v>13001</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="10">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="L4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="9">
-        <v>13001</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="9">
-        <v>1</v>
-      </c>
-      <c r="J4" s="10"/>
-      <c r="L4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:12">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" s="3">
         <v>13002</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="L5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="L5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:12">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3">
         <v>13004</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="9">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10"/>
+      <c r="H6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11"/>
       <c r="L6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1557,25 +1603,25 @@
       <c r="D7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="10">
+        <v>13005</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="9">
-        <v>13005</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="10">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="L7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="L7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:12">
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -1588,25 +1634,25 @@
       <c r="D8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="9">
+        <v>17</v>
+      </c>
+      <c r="G8" s="10">
         <v>13006</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="9">
-        <v>1</v>
-      </c>
-      <c r="J8" s="10"/>
+      <c r="H8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11"/>
       <c r="L8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1617,29 +1663,29 @@
         <v>2000</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="8"/>
+        <v>29</v>
+      </c>
+      <c r="E9" s="10"/>
       <c r="F9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="9">
+        <v>17</v>
+      </c>
+      <c r="G9" s="10">
         <v>13009</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="9">
-        <v>1</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="12">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:12">
+      <c r="H9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="10">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1650,62 +1696,62 @@
         <v>2000</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="10">
+        <v>13011</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="10">
+        <v>13013</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="10">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10" s="9">
-        <v>13011</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="9">
-        <v>1</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:12">
-      <c r="A11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="9">
-        <v>13013</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" s="9">
-        <v>1</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:12">
+      <c r="L11" s="14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1716,29 +1762,26 @@
         <v>2000</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="E12" s="10"/>
       <c r="F12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="9">
+        <v>17</v>
+      </c>
+      <c r="G12" s="10">
         <v>13015</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="9">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:12">
+      <c r="H12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1749,27 +1792,24 @@
         <v>2000</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="8"/>
+        <v>35</v>
+      </c>
+      <c r="E13" s="10"/>
       <c r="F13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="9">
+        <v>17</v>
+      </c>
+      <c r="G13" s="10">
         <v>13017</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="9">
-        <v>1</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="L13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:12">
+      <c r="H13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="10">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1780,29 +1820,29 @@
         <v>2000</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="E14" s="10"/>
       <c r="F14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="9">
+        <v>17</v>
+      </c>
+      <c r="G14" s="10">
         <v>13019</v>
       </c>
-      <c r="H14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="9">
-        <v>1</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>29</v>
+      <c r="H14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="10">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L14" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:12">
+    <row r="15" spans="1:12">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1813,29 +1853,29 @@
         <v>2000</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="8"/>
+        <v>37</v>
+      </c>
+      <c r="E15" s="10"/>
       <c r="F15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="9">
+        <v>17</v>
+      </c>
+      <c r="G15" s="10">
         <v>13021</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="9">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>37</v>
+      <c r="H15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="10">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L15" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:12">
+    <row r="16" spans="1:12">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1846,29 +1886,29 @@
         <v>2000</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="10">
+        <v>13023</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="10">
+        <v>1</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>38</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="9">
-        <v>13023</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="9">
-        <v>1</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>37</v>
       </c>
       <c r="L16" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1879,29 +1919,29 @@
         <v>2000</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="8"/>
+        <v>40</v>
+      </c>
+      <c r="E17" s="10"/>
       <c r="F17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="9">
+        <v>17</v>
+      </c>
+      <c r="G17" s="10">
         <v>13025</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="9">
-        <v>1</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>37</v>
+      <c r="H17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L17" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
@@ -1912,29 +1952,30 @@
         <v>2000</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="E18" s="10"/>
       <c r="F18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="9">
+        <v>17</v>
+      </c>
+      <c r="G18" s="10">
         <v>13027</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="9">
-        <v>1</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="10">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11"/>
       <c r="L18" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:12">
+        <v>1110</v>
+      </c>
+      <c r="M18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
@@ -1945,29 +1986,30 @@
         <v>2000</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="E19" s="10"/>
       <c r="F19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="9">
+        <v>17</v>
+      </c>
+      <c r="G19" s="10">
         <v>13029</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19" s="9">
-        <v>1</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11"/>
       <c r="L19" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:12">
+        <v>1110</v>
+      </c>
+      <c r="M19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -1978,194 +2020,196 @@
         <v>2000</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="10">
+        <v>13034</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="10">
+        <v>13037</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="10">
+        <v>1</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="10">
+        <v>13040</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="10">
+        <v>13043</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="10">
+        <v>13045</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="9">
-        <v>13034</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="9">
-        <v>1</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:12">
-      <c r="A21" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="I24" s="10">
+        <v>1</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="L24" s="3">
+        <v>1310</v>
+      </c>
+      <c r="M24" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="9">
-        <v>13037</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="9">
-        <v>1</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" spans="1:12">
-      <c r="A22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="9">
-        <v>13040</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="9">
-        <v>1</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:12">
-      <c r="A23" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D23" s="9" t="s">
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="10">
+        <v>13047</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1</v>
+      </c>
+      <c r="J25" s="11"/>
+      <c r="L25" s="3">
+        <v>1310</v>
+      </c>
+      <c r="M25" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G23" s="9">
-        <v>13043</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="9">
-        <v>1</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" spans="1:12">
-      <c r="A24" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="9">
-        <v>13045</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="9">
-        <v>1</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:12">
-      <c r="A25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="9">
-        <v>13047</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="9">
-        <v>1</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" spans="1:12">
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -2176,29 +2220,26 @@
         <v>2000</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E26" s="8"/>
+        <v>52</v>
+      </c>
+      <c r="E26" s="10"/>
       <c r="F26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="9">
+        <v>17</v>
+      </c>
+      <c r="G26" s="10">
         <v>13067</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="9">
-        <v>1</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L26" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:12">
+      <c r="H26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="10">
+        <v>1</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
@@ -2209,29 +2250,26 @@
         <v>2000</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" s="8"/>
+        <v>53</v>
+      </c>
+      <c r="E27" s="10"/>
       <c r="F27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="9">
+        <v>17</v>
+      </c>
+      <c r="G27" s="10">
         <v>13069</v>
       </c>
-      <c r="H27" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="9">
-        <v>1</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L27" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" spans="1:12">
+      <c r="H27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="10">
+        <v>1</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
@@ -2242,29 +2280,29 @@
         <v>2000</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="E28" s="10"/>
       <c r="F28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="9">
+        <v>17</v>
+      </c>
+      <c r="G28" s="10">
         <v>13073</v>
       </c>
-      <c r="H28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="9">
-        <v>1</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>51</v>
+      <c r="H28" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="10">
+        <v>1</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="L28" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="1:12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2275,29 +2313,29 @@
         <v>2000</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="8"/>
+        <v>56</v>
+      </c>
+      <c r="E29" s="10"/>
       <c r="F29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="9">
+        <v>17</v>
+      </c>
+      <c r="G29" s="10">
         <v>13075</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="9">
-        <v>1</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>37</v>
+      <c r="H29" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="10">
+        <v>1</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L29" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" spans="1:12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
@@ -2308,29 +2346,29 @@
         <v>2000</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="E30" s="10"/>
       <c r="F30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G30" s="9">
+        <v>17</v>
+      </c>
+      <c r="G30" s="10">
         <v>13077</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="9">
-        <v>1</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>37</v>
+      <c r="H30" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="10">
+        <v>1</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L30" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="7" t="s">
         <v>11</v>
       </c>
@@ -2341,29 +2379,29 @@
         <v>2000</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E31" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="E31" s="10"/>
       <c r="F31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="9">
+        <v>17</v>
+      </c>
+      <c r="G31" s="10">
         <v>13079</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="9">
-        <v>1</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>51</v>
+      <c r="H31" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="L31" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" spans="1:12">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2374,29 +2412,29 @@
         <v>2000</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="E32" s="10"/>
       <c r="F32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="9">
+        <v>17</v>
+      </c>
+      <c r="G32" s="10">
         <v>13081</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="9">
-        <v>1</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>37</v>
+      <c r="H32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="10">
+        <v>1</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L32" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="1:15">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
         <v>11</v>
       </c>
@@ -2407,58 +2445,58 @@
         <v>2000</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="9">
+        <v>60</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="10">
         <v>13083</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="9">
-        <v>1</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>37</v>
+      <c r="H33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="10">
+        <v>1</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="L33" s="3">
-        <v>10000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A34" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="14">
-        <v>2000</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14" t="s">
-        <v>58</v>
+      <c r="A34" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="G34" s="8">
         <v>3301</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="14">
-        <v>1</v>
-      </c>
-      <c r="J34" s="15"/>
-      <c r="L34" s="16"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:15">
+      <c r="H34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="16">
+        <v>1</v>
+      </c>
+      <c r="J34" s="17"/>
+      <c r="L34" s="18"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2469,29 +2507,30 @@
         <v>2000</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E35" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="E35" s="10"/>
       <c r="F35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G35" s="9">
+        <v>17</v>
+      </c>
+      <c r="G35" s="10">
         <v>13085</v>
       </c>
-      <c r="H35" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" s="9">
-        <v>1</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H35" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="10">
+        <v>1</v>
+      </c>
+      <c r="J35" s="11"/>
       <c r="L35" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:15">
+        <v>1710</v>
+      </c>
+      <c r="M35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="7" t="s">
         <v>11</v>
       </c>
@@ -2502,29 +2541,30 @@
         <v>2000</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="E36" s="10"/>
       <c r="F36" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="9">
+        <v>17</v>
+      </c>
+      <c r="G36" s="10">
         <v>13087</v>
       </c>
-      <c r="H36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="9">
-        <v>1</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>29</v>
-      </c>
+      <c r="H36" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1</v>
+      </c>
+      <c r="J36" s="11"/>
       <c r="L36" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:15">
+        <v>1710</v>
+      </c>
+      <c r="M36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2535,29 +2575,29 @@
         <v>2000</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="8"/>
+        <v>65</v>
+      </c>
+      <c r="E37" s="10"/>
       <c r="F37" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="9">
+        <v>17</v>
+      </c>
+      <c r="G37" s="10">
         <v>13091</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I37" s="9">
-        <v>1</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>51</v>
+      <c r="H37" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="10">
+        <v>1</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="L37" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:15">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
         <v>11</v>
       </c>
@@ -2568,29 +2608,29 @@
         <v>2000</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E38" s="8"/>
+        <v>66</v>
+      </c>
+      <c r="E38" s="10"/>
       <c r="F38" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38" s="9">
+        <v>17</v>
+      </c>
+      <c r="G38" s="10">
         <v>13093</v>
       </c>
-      <c r="H38" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="9">
-        <v>1</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>51</v>
+      <c r="H38" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="10">
+        <v>1</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="L38" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:15">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
         <v>11</v>
       </c>
@@ -2601,122 +2641,122 @@
         <v>2000</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E39" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="E39" s="10"/>
       <c r="F39" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G39" s="9">
+        <v>17</v>
+      </c>
+      <c r="G39" s="10">
         <v>13095</v>
       </c>
-      <c r="H39" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="9">
-        <v>1</v>
-      </c>
-      <c r="J39" s="10"/>
-      <c r="L39" s="3" t="s">
+      <c r="H39" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" s="10">
+        <v>1</v>
+      </c>
+      <c r="J39" s="11"/>
+      <c r="L39" s="3">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="10">
+        <v>13097</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="10">
+        <v>1</v>
+      </c>
+      <c r="J40" s="11"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:15">
+      <c r="A41" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" s="10"/>
+      <c r="F41" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="10">
+        <v>4704</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="10">
         <v>20</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:15">
-      <c r="A40" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G40" s="9">
-        <v>13097</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="9">
-        <v>1</v>
-      </c>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A41" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="14">
-        <v>2000</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="9">
-        <v>4704</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I41" s="9">
-        <v>20</v>
-      </c>
-      <c r="J41" s="15"/>
-      <c r="L41" s="16" t="s">
-        <v>66</v>
+      <c r="J41" s="17"/>
+      <c r="L41" s="18" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A42" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="14">
-        <v>2000</v>
+      <c r="A42" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="8">
+        <v>6000</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="8"/>
+        <v>73</v>
+      </c>
+      <c r="E42" s="10"/>
       <c r="F42" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G42" s="8">
         <v>5400</v>
       </c>
-      <c r="H42" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I42" s="9">
+      <c r="H42" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I42" s="10">
         <v>20</v>
       </c>
-      <c r="J42" s="10"/>
-      <c r="L42" s="16" t="s">
-        <v>66</v>
+      <c r="J42" s="11"/>
+      <c r="L42" s="18" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A43" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C43" s="8">
         <v>6000</v>
@@ -2724,734 +2764,809 @@
       <c r="D43" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="8"/>
+      <c r="E43" s="10"/>
       <c r="F43" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43" s="8">
-        <v>2500</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="G43" s="3">
+        <v>596</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>15</v>
       </c>
       <c r="I43" s="8">
         <v>1</v>
       </c>
-      <c r="J43" s="10"/>
-      <c r="L43" s="12"/>
-    </row>
-    <row r="44" ht="14.25" spans="1:15">
+      <c r="J43" s="11"/>
+      <c r="L43" s="14"/>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C44" s="8">
         <v>6000</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E44" s="8"/>
+      <c r="D44" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E44" s="10"/>
       <c r="F44" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G44" s="9">
+        <v>17</v>
+      </c>
+      <c r="G44" s="20">
         <v>12400</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="10">
+        <v>1</v>
+      </c>
+      <c r="J44" s="21"/>
+      <c r="L44" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="9">
-        <v>1</v>
-      </c>
-      <c r="J44" s="18"/>
-      <c r="L44" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:15">
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C45" s="8">
         <v>6000</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="10">
+        <v>12401</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="10">
+        <v>1</v>
+      </c>
+      <c r="J45" s="11"/>
+      <c r="L45" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="9">
-        <v>12401</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I45" s="9">
-        <v>1</v>
-      </c>
-      <c r="J45" s="10"/>
-      <c r="L45" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" spans="1:15">
-      <c r="A46" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="B46" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C46" s="8">
         <v>6000</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="10">
+        <v>12402</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="10">
+        <v>1</v>
+      </c>
+      <c r="J46" s="22"/>
+      <c r="L46" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N46" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46" s="9">
-        <v>12402</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="9">
-        <v>1</v>
-      </c>
-      <c r="J46" s="19"/>
-      <c r="L46" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M46">
-        <v>18</v>
-      </c>
-      <c r="N46" t="s">
-        <v>24</v>
-      </c>
-      <c r="O46" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" spans="1:15">
-      <c r="A47" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="C47" s="8">
         <v>6000</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="8"/>
+      <c r="D47" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="10"/>
       <c r="F47" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="9">
+        <v>17</v>
+      </c>
+      <c r="G47" s="10">
         <v>12404</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="10">
+        <v>1</v>
+      </c>
+      <c r="J47" s="22"/>
+      <c r="L47" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I47" s="9">
-        <v>1</v>
-      </c>
-      <c r="J47" s="19"/>
-      <c r="L47" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M47">
-        <v>32</v>
-      </c>
-      <c r="N47" t="s">
-        <v>24</v>
+      <c r="N47" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="O47" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25" spans="1:15">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C48" s="8">
         <v>6000</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="8"/>
+      <c r="D48" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="10"/>
       <c r="F48" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G48" s="9">
+        <v>17</v>
+      </c>
+      <c r="G48" s="10">
         <v>12405</v>
       </c>
-      <c r="H48" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="9">
-        <v>1</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>29</v>
+      <c r="H48" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="10">
+        <v>1</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L48" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="49" ht="14.25" spans="1:12">
+      <c r="N48" s="23">
+        <v>310</v>
+      </c>
+      <c r="O48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C49" s="8">
         <v>6000</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" s="8"/>
+      <c r="D49" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="10"/>
       <c r="F49" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G49" s="9">
+        <v>17</v>
+      </c>
+      <c r="G49" s="10">
         <v>12406</v>
       </c>
-      <c r="H49" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" s="9">
-        <v>1</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>29</v>
+      <c r="H49" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="10">
+        <v>1</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="50" ht="14.25" spans="1:12">
+      <c r="N49" s="23">
+        <v>320</v>
+      </c>
+      <c r="O49" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C50" s="8">
         <v>6000</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" s="8"/>
+      <c r="D50" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="10"/>
       <c r="F50" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G50" s="9">
+        <v>17</v>
+      </c>
+      <c r="G50" s="10">
         <v>12407</v>
       </c>
-      <c r="H50" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" s="9">
-        <v>1</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>29</v>
+      <c r="H50" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" s="10">
+        <v>1</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L50" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="51" ht="14.25" spans="1:12">
+      <c r="N50" s="23">
+        <v>300</v>
+      </c>
+      <c r="O50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C51" s="8">
         <v>6000</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="8"/>
+      <c r="D51" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="10"/>
       <c r="F51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="10">
+        <v>12408</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="9">
-        <v>12408</v>
-      </c>
-      <c r="H51" s="11" t="s">
+      <c r="I51" s="10">
+        <v>1</v>
+      </c>
+      <c r="J51" s="11"/>
+      <c r="L51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I51" s="9">
-        <v>1</v>
-      </c>
-      <c r="J51" s="10"/>
-      <c r="L51" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" ht="14.25" spans="1:12">
+      <c r="N51" s="23">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C52" s="8">
         <v>6000</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E52" s="8"/>
+      <c r="D52" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E52" s="10"/>
       <c r="F52" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="10">
+        <v>12409</v>
+      </c>
+      <c r="H52" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="9">
-        <v>12409</v>
-      </c>
-      <c r="H52" s="11" t="s">
+      <c r="I52" s="10">
+        <v>1</v>
+      </c>
+      <c r="J52" s="11"/>
+      <c r="L52" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I52" s="9">
-        <v>1</v>
-      </c>
-      <c r="J52" s="10"/>
-      <c r="L52" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" ht="14.25" spans="1:12">
+      <c r="N52" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C53" s="8">
         <v>6000</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E53" s="8"/>
+      <c r="D53" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="10"/>
       <c r="F53" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="9">
+        <v>17</v>
+      </c>
+      <c r="G53" s="10">
         <v>12412</v>
       </c>
-      <c r="H53" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I53" s="9">
-        <v>1</v>
-      </c>
-      <c r="J53" s="10" t="s">
-        <v>31</v>
+      <c r="H53" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" s="10">
+        <v>1</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="L53" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="54" ht="14.25" spans="1:12">
+      <c r="N53" s="23">
+        <v>620</v>
+      </c>
+      <c r="O53" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C54" s="8">
         <v>6000</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" s="8"/>
+      <c r="D54" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="10"/>
       <c r="F54" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G54" s="9">
+        <v>17</v>
+      </c>
+      <c r="G54" s="10">
         <v>12416</v>
       </c>
-      <c r="H54" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I54" s="9">
-        <v>1</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="55" ht="14.25" spans="1:12">
+      <c r="H54" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="10">
+        <v>1</v>
+      </c>
+      <c r="J54" s="11"/>
+      <c r="N54" s="23">
+        <v>640</v>
+      </c>
+      <c r="O54" s="24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C55" s="8">
         <v>6000</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E55" s="8"/>
+      <c r="D55" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="10"/>
       <c r="F55" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="9">
+        <v>17</v>
+      </c>
+      <c r="G55" s="10">
         <v>12418</v>
       </c>
-      <c r="H55" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="9">
-        <v>1</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L55" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" spans="1:12">
+      <c r="H55" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I55" s="10">
+        <v>1</v>
+      </c>
+      <c r="J55" s="11"/>
+      <c r="N55" s="23">
+        <v>640</v>
+      </c>
+      <c r="O55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C56" s="8">
         <v>6000</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E56" s="8"/>
+      <c r="D56" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56" s="10"/>
       <c r="F56" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" s="9">
+        <v>17</v>
+      </c>
+      <c r="G56" s="10">
         <v>12432</v>
       </c>
-      <c r="H56" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I56" s="9">
-        <v>1</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>29</v>
+      <c r="H56" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="10">
+        <v>1</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L56" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="57" ht="14.25" spans="1:12">
+      <c r="N56" s="23">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C57" s="8">
         <v>6000</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E57" s="8"/>
+      <c r="D57" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E57" s="10"/>
       <c r="F57" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G57" s="9">
+        <v>17</v>
+      </c>
+      <c r="G57" s="10">
         <v>12435</v>
       </c>
-      <c r="H57" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I57" s="9">
-        <v>1</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25" spans="1:12">
+      <c r="H57" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" s="10">
+        <v>1</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="23">
+        <v>660</v>
+      </c>
+      <c r="O57" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C58" s="8">
         <v>6000</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E58" s="8"/>
+      <c r="D58" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="10"/>
       <c r="F58" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="9">
+        <v>17</v>
+      </c>
+      <c r="G58" s="10">
         <v>12437</v>
       </c>
-      <c r="H58" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="9">
-        <v>1</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25" spans="1:12">
+      <c r="H58" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" s="10">
+        <v>1</v>
+      </c>
+      <c r="J58" s="11"/>
+      <c r="N58" s="23">
+        <v>680</v>
+      </c>
+      <c r="O58" s="24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C59" s="8">
         <v>6000</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E59" s="8"/>
+      <c r="D59" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="10"/>
       <c r="F59" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="9">
+        <v>17</v>
+      </c>
+      <c r="G59" s="10">
         <v>12439</v>
       </c>
-      <c r="H59" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="9">
-        <v>1</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" spans="1:12">
+      <c r="H59" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="10">
+        <v>1</v>
+      </c>
+      <c r="J59" s="11"/>
+      <c r="N59">
+        <v>680</v>
+      </c>
+      <c r="O59" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C60" s="8">
         <v>6000</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="8"/>
+      <c r="D60" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E60" s="10"/>
       <c r="F60" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G60" s="8">
         <v>12453</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I60" s="8">
         <v>1</v>
       </c>
-      <c r="J60" s="10" t="s">
-        <v>29</v>
+      <c r="J60" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="L60" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="61" ht="14.25" spans="1:12">
-      <c r="A61" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="20">
+      <c r="N60">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" s="25">
         <v>6000</v>
       </c>
-      <c r="D61" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G61" s="20">
+      <c r="D61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E61" s="10"/>
+      <c r="F61" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G61" s="25">
         <v>2501</v>
       </c>
-      <c r="H61" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" s="20">
-        <v>1</v>
-      </c>
-      <c r="J61" s="18"/>
-    </row>
-    <row r="62" ht="14.25" spans="1:12">
+      <c r="H61" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="25">
+        <v>1</v>
+      </c>
+      <c r="J61" s="21"/>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C62" s="8">
         <v>6000</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="10">
+        <v>12457</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" s="10">
+        <v>1</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62">
+        <v>730</v>
+      </c>
+      <c r="O62" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="9">
-        <v>12457</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="9">
-        <v>1</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" ht="14.25" spans="1:12">
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C63" s="8">
         <v>6000</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" s="8"/>
+      <c r="D63" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E63" s="10"/>
       <c r="F63" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="9">
+        <v>17</v>
+      </c>
+      <c r="G63" s="10">
         <v>12461</v>
       </c>
-      <c r="H63" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" s="9">
-        <v>1</v>
-      </c>
-      <c r="J63" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="L63" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" ht="14.25" spans="1:12">
+      <c r="H63" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I63" s="10">
+        <v>1</v>
+      </c>
+      <c r="J63" s="11"/>
+      <c r="N63" s="23">
+        <v>800</v>
+      </c>
+      <c r="O63" s="24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A64" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C64" s="8">
         <v>6000</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" s="8"/>
+        <v>100</v>
+      </c>
+      <c r="E64" s="10"/>
       <c r="F64" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" s="8">
         <v>12463</v>
       </c>
-      <c r="H64" s="8" t="s">
-        <v>23</v>
+      <c r="H64" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="I64" s="8">
         <v>1</v>
       </c>
-      <c r="J64" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L64" s="3">
-        <v>1000</v>
+      <c r="J64" s="8"/>
+      <c r="L64" s="3"/>
+      <c r="N64" s="2">
+        <v>800</v>
+      </c>
+      <c r="O64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25" spans="1:12">
+      <c r="A65" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E65" s="10"/>
+      <c r="F65" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I65" s="10">
+        <v>20</v>
+      </c>
+      <c r="J65" s="11"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="18" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O64" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O65" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:L63">
     <sortCondition ref="G2"/>
   </sortState>
   <conditionalFormatting sqref="D2">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D41:D42">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D43">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D42">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D40 D44:D63 D65:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="D1 D3:D40 D44:D63 D66:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="102">
   <si>
     <t>设备名称</t>
   </si>
@@ -227,7 +227,7 @@
     <t>防尘盖压装位移</t>
   </si>
   <si>
-    <t>扭矩检测值</t>
+    <t>ABS反转齿数</t>
   </si>
   <si>
     <t>ABS检测峰值</t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" ht="14.25" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" ht="14.25" spans="1:12">
       <c r="A4" s="7" t="s">
         <v>11</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" ht="14.25" spans="1:12">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" ht="14.25" spans="1:12">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" ht="14.25" spans="1:12">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" ht="14.25" spans="1:12">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" ht="14.25" spans="1:12">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" ht="14.25" spans="1:12">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" ht="14.25" spans="1:12">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" ht="14.25" spans="1:12">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" ht="14.25" spans="1:12">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" ht="14.25" spans="1:12">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" ht="14.25" spans="1:12">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" ht="14.25" spans="1:12">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" ht="14.25" spans="1:13">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" ht="14.25" spans="1:13">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" ht="14.25" spans="1:13">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" ht="14.25" spans="1:13">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" ht="14.25" spans="1:13">
       <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" ht="14.25" spans="1:13">
       <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" ht="14.25" spans="1:13">
       <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" ht="14.25" spans="1:13">
       <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" ht="14.25" spans="1:13">
       <c r="A25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" ht="14.25" spans="1:13">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" ht="14.25" spans="1:13">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" ht="14.25" spans="1:13">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" ht="14.25" spans="1:13">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" ht="14.25" spans="1:13">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" ht="14.25" spans="1:13">
       <c r="A31" s="7" t="s">
         <v>11</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" ht="14.25" spans="1:13">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" ht="14.25" spans="1:15">
       <c r="A33" s="7" t="s">
         <v>11</v>
       </c>
@@ -2496,7 +2496,7 @@
       <c r="J34" s="17"/>
       <c r="L34" s="18"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" ht="14.25" spans="1:15">
       <c r="A35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" ht="14.25" spans="1:15">
       <c r="A36" s="7" t="s">
         <v>11</v>
       </c>
@@ -2590,14 +2590,12 @@
       <c r="I37" s="10">
         <v>1</v>
       </c>
-      <c r="J37" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="J37" s="11"/>
       <c r="L37" s="3">
         <v>1720</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" ht="14.25" spans="1:15">
       <c r="A38" s="7" t="s">
         <v>11</v>
       </c>
@@ -2630,7 +2628,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" ht="14.25" spans="1:15">
       <c r="A39" s="7" t="s">
         <v>11</v>
       </c>
@@ -2661,7 +2659,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" ht="14.25" spans="1:15">
       <c r="A40" s="7" t="s">
         <v>11</v>
       </c>
@@ -2679,10 +2677,10 @@
         <v>17</v>
       </c>
       <c r="G40" s="10">
-        <v>13097</v>
+        <v>7311</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
@@ -2780,7 +2778,7 @@
       <c r="J43" s="11"/>
       <c r="L43" s="14"/>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" ht="14.25" spans="1:15">
       <c r="A44" s="8" t="s">
         <v>71</v>
       </c>
@@ -2811,7 +2809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" ht="14.25" spans="1:15">
       <c r="A45" s="8" t="s">
         <v>71</v>
       </c>
@@ -2842,7 +2840,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" ht="14.25" spans="1:15">
       <c r="A46" s="8" t="s">
         <v>71</v>
       </c>
@@ -2876,7 +2874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" ht="14.25" spans="1:15">
       <c r="A47" s="8" t="s">
         <v>71</v>
       </c>
@@ -2913,7 +2911,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" ht="14.25" spans="1:15">
       <c r="A48" s="8" t="s">
         <v>71</v>
       </c>
@@ -2952,7 +2950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" ht="14.25" spans="1:15">
       <c r="A49" s="8" t="s">
         <v>71</v>
       </c>
@@ -2991,7 +2989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" ht="14.25" spans="1:15">
       <c r="A50" s="8" t="s">
         <v>71</v>
       </c>
@@ -3030,7 +3028,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" ht="14.25" spans="1:15">
       <c r="A51" s="8" t="s">
         <v>71</v>
       </c>
@@ -3064,7 +3062,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" ht="14.25" spans="1:15">
       <c r="A52" s="8" t="s">
         <v>71</v>
       </c>
@@ -3098,7 +3096,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" ht="14.25" spans="1:15">
       <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
@@ -3137,7 +3135,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" ht="14.25" spans="1:15">
       <c r="A54" s="8" t="s">
         <v>71</v>
       </c>
@@ -3171,7 +3169,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" ht="14.25" spans="1:15">
       <c r="A55" s="8" t="s">
         <v>71</v>
       </c>
@@ -3205,7 +3203,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" ht="14.25" spans="1:15">
       <c r="A56" s="8" t="s">
         <v>71</v>
       </c>
@@ -3241,7 +3239,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" ht="14.25" spans="1:15">
       <c r="A57" s="8" t="s">
         <v>71</v>
       </c>
@@ -3277,7 +3275,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" ht="14.25" spans="1:15">
       <c r="A58" s="8" t="s">
         <v>71</v>
       </c>
@@ -3311,7 +3309,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" ht="14.25" spans="1:15">
       <c r="A59" s="8" t="s">
         <v>71</v>
       </c>
@@ -3345,7 +3343,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" ht="14.25" spans="1:15">
       <c r="A60" s="8" t="s">
         <v>71</v>
       </c>
@@ -3381,7 +3379,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" ht="14.25" spans="1:15">
       <c r="A61" s="25" t="s">
         <v>71</v>
       </c>
@@ -3409,7 +3407,7 @@
       </c>
       <c r="J61" s="21"/>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" ht="14.25" spans="1:15">
       <c r="A62" s="8" t="s">
         <v>71</v>
       </c>
@@ -3445,7 +3443,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" ht="14.25" spans="1:15">
       <c r="A63" s="8" t="s">
         <v>71</v>
       </c>

--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="108">
   <si>
     <t>设备名称</t>
   </si>
@@ -336,6 +336,24 @@
   </si>
   <si>
     <t>内法兰半成品码</t>
+  </si>
+  <si>
+    <t>螺栓压装1</t>
+  </si>
+  <si>
+    <t>螺栓压装2</t>
+  </si>
+  <si>
+    <t>螺栓压装3</t>
+  </si>
+  <si>
+    <t>螺栓压装4</t>
+  </si>
+  <si>
+    <t>螺栓压装5</t>
+  </si>
+  <si>
+    <t>螺栓压装AVG</t>
   </si>
 </sst>
 </file>
@@ -1385,7 +1403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2564,7 +2582,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" ht="14.25" spans="1:15">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2711,7 +2729,7 @@
         <v>70</v>
       </c>
       <c r="I41" s="10">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J41" s="17"/>
       <c r="L41" s="18" t="s">
@@ -2736,13 +2754,13 @@
         <v>17</v>
       </c>
       <c r="G42" s="8">
-        <v>5400</v>
+        <v>4504</v>
       </c>
       <c r="H42" s="19" t="s">
         <v>70</v>
       </c>
       <c r="I42" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J42" s="11"/>
       <c r="L42" s="18" t="s">
@@ -3530,13 +3548,13 @@
         <v>17</v>
       </c>
       <c r="G65" s="3">
-        <v>5500</v>
+        <v>5504</v>
       </c>
       <c r="H65" s="19" t="s">
         <v>70</v>
       </c>
       <c r="I65" s="10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J65" s="11"/>
       <c r="K65" s="2"/>
@@ -3544,27 +3562,204 @@
         <v>70</v>
       </c>
     </row>
+    <row r="66" ht="14.25" spans="1:12">
+      <c r="A66" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="3">
+        <v>5520</v>
+      </c>
+      <c r="H66" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" s="8">
+        <v>1</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25" spans="1:12">
+      <c r="A67" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="3">
+        <v>5521</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" s="8">
+        <v>1</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25" spans="1:12">
+      <c r="A68" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="3">
+        <v>5522</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" s="8">
+        <v>1</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25" spans="1:12">
+      <c r="A69" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" s="3">
+        <v>5523</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" s="8">
+        <v>1</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25" spans="1:12">
+      <c r="A70" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="3">
+        <v>5524</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="8">
+        <v>1</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" spans="1:12">
+      <c r="A71" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="8">
+        <v>6000</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="3">
+        <v>5525</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" s="8">
+        <v>1</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O65" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:L63">
     <sortCondition ref="G2"/>
   </sortState>
   <conditionalFormatting sqref="D2">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D43">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D65">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D43">
+  <conditionalFormatting sqref="D41:D42">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D65">
+  <conditionalFormatting sqref="D66:D71">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D42">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1 D3:D40 D44:D63 D66:D1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="D1 D3:D40 D44:D63 D72:D1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7695"/>
+    <workbookView windowWidth="9225" windowHeight="5145"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -80,12 +80,30 @@
     <t>Boolean</t>
   </si>
   <si>
+    <t>采集结束</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>序列码</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>ABS检测齿数</t>
+  </si>
+  <si>
+    <t>Int16</t>
+  </si>
+  <si>
     <t>托盘号B</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>UInt16</t>
   </si>
   <si>
@@ -107,9 +125,6 @@
     <t>NG代码B</t>
   </si>
   <si>
-    <t>Int16</t>
-  </si>
-  <si>
     <t>A线托盘编号</t>
   </si>
   <si>
@@ -215,12 +230,6 @@
     <t>振动上RH</t>
   </si>
   <si>
-    <t>采集结束</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>防尘盖压装压力</t>
   </si>
   <si>
@@ -234,15 +243,6 @@
   </si>
   <si>
     <t>ABS检测谷值</t>
-  </si>
-  <si>
-    <t>ABS检测齿数</t>
-  </si>
-  <si>
-    <t>序列码</t>
-  </si>
-  <si>
-    <t>String</t>
   </si>
   <si>
     <t>A线</t>
@@ -1004,7 +1004,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1041,25 +1041,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
@@ -1421,7 +1427,7 @@
     <col min="14" max="14" width="25.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:12">
+    <row r="1" ht="14.25" spans="1:15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1456,7 +1462,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:12">
+    <row r="2" ht="14.25" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1484,69 +1490,75 @@
       </c>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" ht="14.25" spans="1:12">
-      <c r="A3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="9" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="10">
-        <v>13000</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="G3" s="8">
+        <v>3301</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="13">
+        <v>1</v>
+      </c>
+      <c r="J3" s="15"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="10">
-        <v>1</v>
-      </c>
-      <c r="J3" s="6"/>
-      <c r="L3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:12">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="10">
+        <v>4704</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="10">
-        <v>13001</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>18</v>
-      </c>
       <c r="I4" s="10">
-        <v>1</v>
-      </c>
-      <c r="J4" s="11"/>
-      <c r="L4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1556,59 +1568,56 @@
       <c r="C5" s="8">
         <v>2000</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="E5" s="10"/>
       <c r="F5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3">
-        <v>13002</v>
-      </c>
-      <c r="H5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="14">
+        <v>7311</v>
+      </c>
+      <c r="H5" s="18" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="10">
         <v>1</v>
       </c>
       <c r="J5" s="11"/>
-      <c r="L5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:12">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3">
-        <v>13004</v>
-      </c>
-      <c r="H6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="14">
+        <v>13000</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="10">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="L6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="10">
-        <v>1</v>
-      </c>
-      <c r="J6" s="11"/>
-      <c r="L6" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:12">
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1623,23 +1632,23 @@
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10">
-        <v>13005</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>18</v>
+        <v>13001</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="I7" s="10">
         <v>1</v>
       </c>
       <c r="J7" s="11"/>
       <c r="L7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -1654,12 +1663,12 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="10">
-        <v>13006</v>
-      </c>
-      <c r="H8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="8">
+        <v>13002</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>28</v>
       </c>
       <c r="I8" s="10">
@@ -1667,10 +1676,10 @@
       </c>
       <c r="J8" s="11"/>
       <c r="L8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="1:12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1681,29 +1690,27 @@
         <v>2000</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="10">
-        <v>13009</v>
-      </c>
-      <c r="H9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="8">
+        <v>13004</v>
+      </c>
+      <c r="H9" s="18" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="10">
         <v>1</v>
       </c>
-      <c r="J9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="14">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" spans="1:12">
+      <c r="J9" s="11"/>
+      <c r="L9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1718,58 +1725,54 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="10">
-        <v>13011</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>22</v>
+        <v>13005</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="I10" s="10">
         <v>1</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="11"/>
+      <c r="L10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>32</v>
-      </c>
-      <c r="L10" s="14">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:12">
-      <c r="A11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G11" s="10">
-        <v>13013</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>22</v>
+        <v>13006</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="I11" s="10">
         <v>1</v>
       </c>
-      <c r="J11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="14">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:12">
+      <c r="J11" s="11"/>
+      <c r="L11" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1784,22 +1787,25 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="10">
-        <v>13015</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>22</v>
+        <v>13009</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I12" s="10">
         <v>1</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:12">
+        <v>35</v>
+      </c>
+      <c r="L12" s="20">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1810,24 +1816,29 @@
         <v>2000</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>13017</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>22</v>
+        <v>13011</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I13" s="10">
         <v>1</v>
       </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:12">
+      <c r="J13" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="20">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1838,29 +1849,29 @@
         <v>2000</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G14" s="10">
-        <v>13019</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>22</v>
+        <v>13013</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I14" s="10">
         <v>1</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:12">
+        <v>35</v>
+      </c>
+      <c r="L14" s="20">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1871,29 +1882,26 @@
         <v>2000</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G15" s="10">
-        <v>13021</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>22</v>
+        <v>13015</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I15" s="10">
         <v>1</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1904,29 +1912,24 @@
         <v>2000</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10">
-        <v>13023</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>22</v>
+        <v>13017</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I16" s="10">
         <v>1</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L16" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:13">
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1937,29 +1940,29 @@
         <v>2000</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="10">
-        <v>13025</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>22</v>
+        <v>13019</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L17" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
@@ -1970,30 +1973,29 @@
         <v>2000</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="10">
-        <v>13027</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>42</v>
+        <v>13021</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I18" s="10">
         <v>1</v>
       </c>
-      <c r="J18" s="11"/>
+      <c r="J18" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="L18" s="3">
-        <v>1110</v>
-      </c>
-      <c r="M18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2008,59 +2010,58 @@
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="10">
-        <v>13029</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>42</v>
+        <v>13023</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
       </c>
-      <c r="J19" s="11"/>
+      <c r="J19" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="L19" s="3">
-        <v>1110</v>
-      </c>
-      <c r="M19" t="s">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:13">
-      <c r="A20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>46</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="10">
-        <v>13034</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>25</v>
+        <v>13025</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I20" s="10">
         <v>1</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L20" s="3">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
@@ -2071,29 +2072,30 @@
         <v>2000</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" s="10">
-        <v>13037</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>25</v>
+        <v>13027</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
       </c>
-      <c r="J21" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="J21" s="11"/>
       <c r="L21" s="3">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" spans="1:13">
+        <v>1110</v>
+      </c>
+      <c r="M21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
@@ -2104,29 +2106,30 @@
         <v>2000</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="10">
-        <v>13040</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>25</v>
+        <v>13029</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I22" s="10">
         <v>1</v>
       </c>
-      <c r="J22" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="J22" s="11"/>
       <c r="L22" s="3">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:13">
+        <v>1110</v>
+      </c>
+      <c r="M22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
@@ -2137,29 +2140,29 @@
         <v>2000</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="10">
-        <v>13043</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>25</v>
+        <v>13034</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I23" s="10">
         <v>1</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L23" s="3">
         <v>1120</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:13">
+    <row r="24" spans="1:13">
       <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
@@ -2170,30 +2173,29 @@
         <v>2000</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G24" s="10">
-        <v>13045</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>42</v>
+        <v>13037</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I24" s="10">
         <v>1</v>
       </c>
-      <c r="J24" s="11"/>
+      <c r="J24" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="L24" s="3">
-        <v>1310</v>
-      </c>
-      <c r="M24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:13">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2204,30 +2206,29 @@
         <v>2000</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="10">
-        <v>13047</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>42</v>
+        <v>13040</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I25" s="10">
         <v>1</v>
       </c>
-      <c r="J25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="L25" s="3">
-        <v>1310</v>
-      </c>
-      <c r="M25" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" spans="1:13">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -2238,26 +2239,29 @@
         <v>2000</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" s="10">
-        <v>13067</v>
-      </c>
-      <c r="H26" s="13" t="s">
+        <v>13043</v>
+      </c>
+      <c r="H26" s="18" t="s">
         <v>22</v>
       </c>
       <c r="I26" s="10">
         <v>1</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:13">
+        <v>35</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
@@ -2268,26 +2272,30 @@
         <v>2000</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G27" s="10">
-        <v>13069</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>22</v>
+        <v>13045</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I27" s="10">
         <v>1</v>
       </c>
-      <c r="J27" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" spans="1:13">
+      <c r="J27" s="11"/>
+      <c r="L27" s="3">
+        <v>1310</v>
+      </c>
+      <c r="M27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
@@ -2298,29 +2306,30 @@
         <v>2000</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E28" s="10"/>
       <c r="F28" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G28" s="10">
-        <v>13073</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>22</v>
+        <v>13047</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I28" s="10">
         <v>1</v>
       </c>
-      <c r="J28" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="J28" s="11"/>
       <c r="L28" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="1:13">
+        <v>1310</v>
+      </c>
+      <c r="M28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2331,29 +2340,26 @@
         <v>2000</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G29" s="10">
-        <v>13075</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>22</v>
+        <v>13067</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I29" s="10">
         <v>1</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L29" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
@@ -2364,29 +2370,26 @@
         <v>2000</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G30" s="10">
-        <v>13077</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>22</v>
+        <v>13069</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I30" s="10">
         <v>1</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L30" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:13">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="7" t="s">
         <v>11</v>
       </c>
@@ -2397,29 +2400,29 @@
         <v>2000</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G31" s="10">
-        <v>13079</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>13073</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I31" s="10">
         <v>1</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L31" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:13">
+    <row r="32" spans="1:13">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2430,29 +2433,29 @@
         <v>2000</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E32" s="10"/>
       <c r="F32" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G32" s="10">
-        <v>13081</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>22</v>
+        <v>13075</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I32" s="10">
         <v>1</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="1:15">
+    <row r="33" spans="1:15">
       <c r="A33" s="7" t="s">
         <v>11</v>
       </c>
@@ -2463,58 +2466,66 @@
         <v>2000</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E33" s="10"/>
-      <c r="F33" s="10" t="s">
-        <v>17</v>
+      <c r="F33" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="G33" s="10">
-        <v>13083</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>22</v>
+        <v>13077</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I33" s="10">
         <v>1</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L33" s="3">
         <v>1600</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A34" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="16">
-        <v>2000</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>61</v>
+      <c r="A34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="8">
-        <v>3301</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" s="16">
-        <v>1</v>
-      </c>
-      <c r="J34" s="17"/>
-      <c r="L34" s="18"/>
-    </row>
-    <row r="35" ht="14.25" spans="1:15">
+      <c r="F34" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34" s="10">
+        <v>13079</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2525,64 +2536,62 @@
         <v>2000</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G35" s="10">
-        <v>13085</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>42</v>
+        <v>13081</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I35" s="10">
         <v>1</v>
       </c>
-      <c r="J35" s="11"/>
+      <c r="J35" s="11" t="s">
+        <v>43</v>
+      </c>
       <c r="L35" s="3">
-        <v>1710</v>
-      </c>
-      <c r="M35" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36" s="10">
+        <v>13083</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="10">
+        <v>1</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:15">
-      <c r="A36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G36" s="10">
-        <v>13087</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="I36" s="10">
-        <v>1</v>
-      </c>
-      <c r="J36" s="11"/>
       <c r="L36" s="3">
-        <v>1710</v>
-      </c>
-      <c r="M36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:15">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2593,27 +2602,30 @@
         <v>2000</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G37" s="10">
-        <v>13091</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>22</v>
+        <v>13085</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I37" s="10">
         <v>1</v>
       </c>
       <c r="J37" s="11"/>
       <c r="L37" s="3">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:15">
+        <v>1710</v>
+      </c>
+      <c r="M37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="7" t="s">
         <v>11</v>
       </c>
@@ -2624,29 +2636,30 @@
         <v>2000</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E38" s="10"/>
       <c r="F38" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G38" s="10">
-        <v>13093</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>25</v>
+        <v>13087</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I38" s="10">
         <v>1</v>
       </c>
-      <c r="J38" s="11" t="s">
-        <v>55</v>
-      </c>
+      <c r="J38" s="11"/>
       <c r="L38" s="3">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:15">
+        <v>1710</v>
+      </c>
+      <c r="M38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="7" t="s">
         <v>11</v>
       </c>
@@ -2657,17 +2670,17 @@
         <v>2000</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G39" s="10">
-        <v>13095</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>25</v>
+        <v>13091</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I39" s="10">
         <v>1</v>
@@ -2677,7 +2690,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="40" ht="14.25" spans="1:15">
+    <row r="40" spans="1:15">
       <c r="A40" s="7" t="s">
         <v>11</v>
       </c>
@@ -2687,60 +2700,69 @@
       <c r="C40" s="8">
         <v>2000</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>68</v>
+      <c r="D40" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G40" s="10">
-        <v>7311</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>25</v>
+        <v>13093</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I40" s="10">
         <v>1</v>
       </c>
-      <c r="J40" s="11"/>
+      <c r="J40" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="3">
+        <v>1720</v>
+      </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A41" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="16">
-        <v>2000</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>69</v>
+      <c r="A41" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="E41" s="10"/>
-      <c r="F41" s="15" t="s">
-        <v>17</v>
+      <c r="F41" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="G41" s="10">
-        <v>4704</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>70</v>
+        <v>13095</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I41" s="10">
-        <v>34</v>
-      </c>
-      <c r="J41" s="17"/>
-      <c r="L41" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" s="2" customFormat="1" ht="14.25" spans="1:15">
-      <c r="A42" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="3">
+        <v>1720</v>
+      </c>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+      <c r="A42" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C42" s="8">
@@ -2751,23 +2773,23 @@
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G42" s="8">
-        <v>4504</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>70</v>
+        <v>12484</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="I42" s="10">
         <v>10</v>
       </c>
       <c r="J42" s="11"/>
-      <c r="L42" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="14.25" spans="1:15">
+      <c r="L42" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
       <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
@@ -2787,16 +2809,16 @@
       <c r="G43" s="3">
         <v>596</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="22" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="8">
         <v>1</v>
       </c>
       <c r="J43" s="11"/>
-      <c r="L43" s="14"/>
-    </row>
-    <row r="44" ht="14.25" spans="1:15">
+      <c r="L43" s="20"/>
+    </row>
+    <row r="44" hidden="1" spans="1:15">
       <c r="A44" s="8" t="s">
         <v>71</v>
       </c>
@@ -2811,23 +2833,23 @@
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="20">
+        <v>19</v>
+      </c>
+      <c r="G44" s="22">
         <v>12400</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H44" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="10">
+        <v>1</v>
+      </c>
+      <c r="J44" s="23"/>
+      <c r="L44" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I44" s="10">
-        <v>1</v>
-      </c>
-      <c r="J44" s="21"/>
-      <c r="L44" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:15">
+    </row>
+    <row r="45" hidden="1" spans="1:15">
       <c r="A45" s="8" t="s">
         <v>71</v>
       </c>
@@ -2842,23 +2864,23 @@
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G45" s="10">
         <v>12401</v>
       </c>
-      <c r="H45" s="13" t="s">
-        <v>25</v>
+      <c r="H45" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I45" s="10">
         <v>1</v>
       </c>
       <c r="J45" s="11"/>
       <c r="L45" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" spans="1:15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" spans="1:15">
       <c r="A46" s="8" t="s">
         <v>71</v>
       </c>
@@ -2873,26 +2895,26 @@
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G46" s="10">
         <v>12402</v>
       </c>
-      <c r="H46" s="13" t="s">
-        <v>22</v>
+      <c r="H46" s="18" t="s">
+        <v>28</v>
       </c>
       <c r="I46" s="10">
         <v>1</v>
       </c>
-      <c r="J46" s="22"/>
+      <c r="J46" s="24"/>
       <c r="L46" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N46" s="23" t="s">
+      <c r="N46" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="47" ht="14.25" spans="1:15">
+    <row r="47" hidden="1" spans="1:15">
       <c r="A47" s="8" t="s">
         <v>71</v>
       </c>
@@ -2907,29 +2929,29 @@
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G47" s="10">
         <v>12404</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="H47" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="10">
+        <v>1</v>
+      </c>
+      <c r="J47" s="24"/>
+      <c r="L47" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I47" s="10">
-        <v>1</v>
-      </c>
-      <c r="J47" s="22"/>
-      <c r="L47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N47" s="23" t="s">
+      <c r="N47" s="25" t="s">
         <v>80</v>
       </c>
       <c r="O47" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="48" ht="14.25" spans="1:15">
+    <row r="48" hidden="1" spans="1:15">
       <c r="A48" s="8" t="s">
         <v>71</v>
       </c>
@@ -2944,31 +2966,31 @@
       </c>
       <c r="E48" s="10"/>
       <c r="F48" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G48" s="10">
         <v>12405</v>
       </c>
-      <c r="H48" s="13" t="s">
-        <v>25</v>
+      <c r="H48" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I48" s="10">
         <v>1</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="23">
+      <c r="N48" s="25">
         <v>310</v>
       </c>
       <c r="O48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25" spans="1:15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:15">
       <c r="A49" s="8" t="s">
         <v>71</v>
       </c>
@@ -2983,31 +3005,31 @@
       </c>
       <c r="E49" s="10"/>
       <c r="F49" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G49" s="10">
         <v>12406</v>
       </c>
-      <c r="H49" s="13" t="s">
-        <v>25</v>
+      <c r="H49" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I49" s="10">
         <v>1</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="N49" s="23">
+      <c r="N49" s="25">
         <v>320</v>
       </c>
       <c r="O49" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="50" ht="14.25" spans="1:15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:15">
       <c r="A50" s="8" t="s">
         <v>71</v>
       </c>
@@ -3022,31 +3044,31 @@
       </c>
       <c r="E50" s="10"/>
       <c r="F50" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G50" s="10">
         <v>12407</v>
       </c>
-      <c r="H50" s="13" t="s">
-        <v>25</v>
+      <c r="H50" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I50" s="10">
         <v>1</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L50" s="3">
         <v>1000</v>
       </c>
-      <c r="N50" s="23">
+      <c r="N50" s="25">
         <v>300</v>
       </c>
       <c r="O50" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25" spans="1:15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:15">
       <c r="A51" s="8" t="s">
         <v>71</v>
       </c>
@@ -3061,26 +3083,26 @@
       </c>
       <c r="E51" s="10"/>
       <c r="F51" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G51" s="10">
         <v>12408</v>
       </c>
-      <c r="H51" s="12" t="s">
-        <v>18</v>
+      <c r="H51" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="I51" s="10">
         <v>1</v>
       </c>
       <c r="J51" s="11"/>
       <c r="L51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N51" s="23">
+        <v>25</v>
+      </c>
+      <c r="N51" s="25">
         <v>460</v>
       </c>
     </row>
-    <row r="52" ht="14.25" spans="1:15">
+    <row r="52" hidden="1" spans="1:15">
       <c r="A52" s="8" t="s">
         <v>71</v>
       </c>
@@ -3095,26 +3117,26 @@
       </c>
       <c r="E52" s="10"/>
       <c r="F52" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G52" s="10">
         <v>12409</v>
       </c>
-      <c r="H52" s="12" t="s">
-        <v>18</v>
+      <c r="H52" s="19" t="s">
+        <v>24</v>
       </c>
       <c r="I52" s="10">
         <v>1</v>
       </c>
       <c r="J52" s="11"/>
       <c r="L52" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N52" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" s="25" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="53" ht="14.25" spans="1:15">
+    <row r="53" hidden="1" spans="1:15">
       <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
@@ -3129,31 +3151,31 @@
       </c>
       <c r="E53" s="10"/>
       <c r="F53" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G53" s="10">
         <v>12412</v>
       </c>
-      <c r="H53" s="13" t="s">
-        <v>25</v>
+      <c r="H53" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I53" s="10">
         <v>1</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L53" s="3">
         <v>100</v>
       </c>
-      <c r="N53" s="23">
+      <c r="N53" s="25">
         <v>620</v>
       </c>
       <c r="O53" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="1:15">
+    <row r="54" hidden="1" spans="1:15">
       <c r="A54" s="8" t="s">
         <v>71</v>
       </c>
@@ -3168,26 +3190,26 @@
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G54" s="10">
         <v>12416</v>
       </c>
-      <c r="H54" s="13" t="s">
-        <v>42</v>
+      <c r="H54" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I54" s="10">
         <v>1</v>
       </c>
       <c r="J54" s="11"/>
-      <c r="N54" s="23">
+      <c r="N54" s="25">
         <v>640</v>
       </c>
-      <c r="O54" s="24" t="s">
+      <c r="O54" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="55" ht="14.25" spans="1:15">
+    <row r="55" hidden="1" spans="1:15">
       <c r="A55" s="8" t="s">
         <v>71</v>
       </c>
@@ -3202,26 +3224,26 @@
       </c>
       <c r="E55" s="10"/>
       <c r="F55" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G55" s="10">
         <v>12418</v>
       </c>
-      <c r="H55" s="13" t="s">
-        <v>42</v>
+      <c r="H55" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I55" s="10">
         <v>1</v>
       </c>
       <c r="J55" s="11"/>
-      <c r="N55" s="23">
+      <c r="N55" s="25">
         <v>640</v>
       </c>
       <c r="O55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" ht="14.25" spans="1:15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" hidden="1" spans="1:15">
       <c r="A56" s="8" t="s">
         <v>71</v>
       </c>
@@ -3236,28 +3258,28 @@
       </c>
       <c r="E56" s="10"/>
       <c r="F56" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G56" s="10">
         <v>12432</v>
       </c>
-      <c r="H56" s="13" t="s">
-        <v>25</v>
+      <c r="H56" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I56" s="10">
         <v>1</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L56" s="3">
         <v>1000</v>
       </c>
-      <c r="N56" s="23">
+      <c r="N56" s="25">
         <v>650</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="1:15">
+    <row r="57" hidden="1" spans="1:15">
       <c r="A57" s="8" t="s">
         <v>71</v>
       </c>
@@ -3272,28 +3294,28 @@
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G57" s="10">
         <v>12435</v>
       </c>
-      <c r="H57" s="13" t="s">
-        <v>25</v>
+      <c r="H57" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I57" s="10">
         <v>1</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N57" s="23">
+        <v>60</v>
+      </c>
+      <c r="N57" s="25">
         <v>660</v>
       </c>
       <c r="O57" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="58" ht="14.25" spans="1:15">
+    <row r="58" hidden="1" spans="1:15">
       <c r="A58" s="8" t="s">
         <v>71</v>
       </c>
@@ -3308,26 +3330,26 @@
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G58" s="10">
         <v>12437</v>
       </c>
-      <c r="H58" s="13" t="s">
-        <v>42</v>
+      <c r="H58" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I58" s="10">
         <v>1</v>
       </c>
       <c r="J58" s="11"/>
-      <c r="N58" s="23">
+      <c r="N58" s="25">
         <v>680</v>
       </c>
-      <c r="O58" s="24" t="s">
+      <c r="O58" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="1:15">
+    <row r="59" hidden="1" spans="1:15">
       <c r="A59" s="8" t="s">
         <v>71</v>
       </c>
@@ -3342,13 +3364,13 @@
       </c>
       <c r="E59" s="10"/>
       <c r="F59" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G59" s="10">
         <v>12439</v>
       </c>
-      <c r="H59" s="13" t="s">
-        <v>42</v>
+      <c r="H59" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I59" s="10">
         <v>1</v>
@@ -3358,10 +3380,10 @@
         <v>680</v>
       </c>
       <c r="O59" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="60" ht="14.25" spans="1:15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" hidden="1" spans="1:15">
       <c r="A60" s="8" t="s">
         <v>71</v>
       </c>
@@ -3371,24 +3393,24 @@
       <c r="C60" s="8">
         <v>6000</v>
       </c>
-      <c r="D60" s="16" t="s">
+      <c r="D60" s="13" t="s">
         <v>97</v>
       </c>
       <c r="E60" s="10"/>
       <c r="F60" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G60" s="8">
         <v>12453</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I60" s="8">
         <v>1</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L60" s="3">
         <v>1000</v>
@@ -3397,35 +3419,35 @@
         <v>690</v>
       </c>
     </row>
-    <row r="61" ht="14.25" spans="1:15">
-      <c r="A61" s="25" t="s">
+    <row r="61" hidden="1" spans="1:15">
+      <c r="A61" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C61" s="27">
         <v>6000</v>
       </c>
-      <c r="D61" s="16" t="s">
-        <v>61</v>
+      <c r="D61" s="13" t="s">
+        <v>16</v>
       </c>
       <c r="E61" s="10"/>
-      <c r="F61" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G61" s="25">
+      <c r="F61" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="27">
         <v>2501</v>
       </c>
-      <c r="H61" s="20" t="s">
+      <c r="H61" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="I61" s="25">
-        <v>1</v>
-      </c>
-      <c r="J61" s="21"/>
-    </row>
-    <row r="62" ht="14.25" spans="1:15">
+      <c r="I61" s="27">
+        <v>1</v>
+      </c>
+      <c r="J61" s="23"/>
+    </row>
+    <row r="62" hidden="1" spans="1:15">
       <c r="A62" s="8" t="s">
         <v>71</v>
       </c>
@@ -3440,19 +3462,19 @@
       </c>
       <c r="E62" s="10"/>
       <c r="F62" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G62" s="10">
         <v>12457</v>
       </c>
-      <c r="H62" s="13" t="s">
-        <v>25</v>
+      <c r="H62" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I62" s="10">
         <v>1</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N62">
         <v>730</v>
@@ -3461,7 +3483,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" ht="14.25" spans="1:15">
+    <row r="63" hidden="1" spans="1:15">
       <c r="A63" s="8" t="s">
         <v>71</v>
       </c>
@@ -3476,26 +3498,26 @@
       </c>
       <c r="E63" s="10"/>
       <c r="F63" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G63" s="10">
         <v>12461</v>
       </c>
-      <c r="H63" s="13" t="s">
-        <v>42</v>
+      <c r="H63" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I63" s="10">
         <v>1</v>
       </c>
       <c r="J63" s="11"/>
-      <c r="N63" s="23">
+      <c r="N63" s="25">
         <v>800</v>
       </c>
-      <c r="O63" s="24" t="s">
+      <c r="O63" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="14.25" spans="1:15">
+    <row r="64" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
       <c r="A64" s="8" t="s">
         <v>71</v>
       </c>
@@ -3510,13 +3532,13 @@
       </c>
       <c r="E64" s="10"/>
       <c r="F64" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G64" s="8">
         <v>12463</v>
       </c>
-      <c r="H64" s="13" t="s">
-        <v>42</v>
+      <c r="H64" s="18" t="s">
+        <v>47</v>
       </c>
       <c r="I64" s="8">
         <v>1</v>
@@ -3527,14 +3549,14 @@
         <v>800</v>
       </c>
       <c r="O64" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" ht="14.25" spans="1:12">
-      <c r="A65" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25" hidden="1" spans="1:12">
+      <c r="A65" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C65" s="8">
@@ -3545,28 +3567,28 @@
       </c>
       <c r="E65" s="10"/>
       <c r="F65" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G65" s="3">
-        <v>5504</v>
-      </c>
-      <c r="H65" s="19" t="s">
-        <v>70</v>
+        <v>12474</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>20</v>
       </c>
       <c r="I65" s="10">
         <v>10</v>
       </c>
       <c r="J65" s="11"/>
       <c r="K65" s="2"/>
-      <c r="L65" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="66" ht="14.25" spans="1:12">
-      <c r="A66" s="15" t="s">
+      <c r="L65" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25" hidden="1" spans="1:12">
+      <c r="A66" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B66" s="16" t="s">
+      <c r="B66" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="8">
@@ -3576,26 +3598,26 @@
         <v>102</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G66" s="3">
         <v>5520</v>
       </c>
-      <c r="H66" s="13" t="s">
-        <v>25</v>
+      <c r="H66" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I66" s="8">
         <v>1</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="67" ht="14.25" spans="1:12">
-      <c r="A67" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" hidden="1" spans="1:12">
+      <c r="A67" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C67" s="8">
@@ -3605,26 +3627,26 @@
         <v>103</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G67" s="3">
         <v>5521</v>
       </c>
-      <c r="H67" s="13" t="s">
-        <v>25</v>
+      <c r="H67" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I67" s="8">
         <v>1</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" ht="14.25" spans="1:12">
-      <c r="A68" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" hidden="1" spans="1:12">
+      <c r="A68" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C68" s="8">
@@ -3634,26 +3656,26 @@
         <v>104</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G68" s="3">
         <v>5522</v>
       </c>
-      <c r="H68" s="13" t="s">
-        <v>25</v>
+      <c r="H68" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I68" s="8">
         <v>1</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="69" ht="14.25" spans="1:12">
-      <c r="A69" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" hidden="1" spans="1:12">
+      <c r="A69" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C69" s="8">
@@ -3663,26 +3685,26 @@
         <v>105</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G69" s="3">
         <v>5523</v>
       </c>
-      <c r="H69" s="13" t="s">
-        <v>25</v>
+      <c r="H69" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I69" s="8">
         <v>1</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="70" ht="14.25" spans="1:12">
-      <c r="A70" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" hidden="1" spans="1:12">
+      <c r="A70" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C70" s="8">
@@ -3692,26 +3714,26 @@
         <v>106</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G70" s="3">
         <v>5524</v>
       </c>
-      <c r="H70" s="13" t="s">
-        <v>25</v>
+      <c r="H70" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I70" s="8">
         <v>1</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="71" ht="14.25" spans="1:12">
-      <c r="A71" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25" hidden="1" spans="1:12">
+      <c r="A71" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C71" s="8">
@@ -3721,23 +3743,31 @@
         <v>107</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G71" s="3">
         <v>5525</v>
       </c>
-      <c r="H71" s="13" t="s">
-        <v>25</v>
+      <c r="H71" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="I71" s="8">
         <v>1</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="B线"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A2:O71">
+      <sortCondition ref="G2"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <sortState ref="A2:L63">

--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="9225" windowHeight="5145"/>
+    <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="110">
   <si>
     <t>设备名称</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>螺栓压装AVG</t>
+  </si>
+  <si>
+    <t>B托盘绑定</t>
+  </si>
+  <si>
+    <t>A托盘绑定</t>
   </si>
 </sst>
 </file>
@@ -1408,8 +1414,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:O71"/>
+  <sheetPr/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -1462,7 +1468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:15">
+    <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -1490,7 +1496,7 @@
       </c>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" ht="14.25" spans="1:15">
       <c r="A3" s="12" t="s">
         <v>11</v>
       </c>
@@ -1523,7 +1529,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" ht="14.25" spans="1:15">
       <c r="A4" s="12" t="s">
         <v>11</v>
       </c>
@@ -1558,7 +1564,7 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" ht="14.25" spans="1:15">
       <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1586,7 +1592,7 @@
       </c>
       <c r="J5" s="11"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" ht="14.25" spans="1:15">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
@@ -1617,7 +1623,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" ht="14.25" spans="1:15">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -1648,7 +1654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" ht="14.25" spans="1:15">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -1679,7 +1685,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" ht="14.25" spans="1:15">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1710,7 +1716,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" ht="14.25" spans="1:15">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
@@ -1741,7 +1747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" ht="14.25" spans="1:15">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" ht="14.25" spans="1:15">
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" ht="14.25" spans="1:15">
       <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1838,7 +1844,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" ht="14.25" spans="1:15">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
@@ -1871,7 +1877,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" ht="14.25" spans="1:15">
       <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
@@ -1901,7 +1907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" ht="14.25" spans="1:15">
       <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
@@ -1929,7 +1935,7 @@
       </c>
       <c r="J16" s="11"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" ht="14.25" spans="1:13">
       <c r="A17" s="7" t="s">
         <v>11</v>
       </c>
@@ -1962,7 +1968,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" ht="14.25" spans="1:13">
       <c r="A18" s="7" t="s">
         <v>11</v>
       </c>
@@ -1995,7 +2001,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" ht="14.25" spans="1:13">
       <c r="A19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" ht="14.25" spans="1:13">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -2061,7 +2067,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" ht="14.25" spans="1:13">
       <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
@@ -2095,7 +2101,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" ht="14.25" spans="1:13">
       <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
@@ -2129,7 +2135,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" ht="14.25" spans="1:13">
       <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
@@ -2162,7 +2168,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" ht="14.25" spans="1:13">
       <c r="A24" s="7" t="s">
         <v>11</v>
       </c>
@@ -2195,7 +2201,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" ht="14.25" spans="1:13">
       <c r="A25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2228,7 +2234,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" ht="14.25" spans="1:13">
       <c r="A26" s="7" t="s">
         <v>11</v>
       </c>
@@ -2261,7 +2267,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" ht="14.25" spans="1:13">
       <c r="A27" s="7" t="s">
         <v>11</v>
       </c>
@@ -2295,7 +2301,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" ht="14.25" spans="1:13">
       <c r="A28" s="7" t="s">
         <v>11</v>
       </c>
@@ -2329,7 +2335,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" ht="14.25" spans="1:13">
       <c r="A29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2359,7 +2365,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" ht="14.25" spans="1:13">
       <c r="A30" s="7" t="s">
         <v>11</v>
       </c>
@@ -2389,7 +2395,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" ht="14.25" spans="1:13">
       <c r="A31" s="7" t="s">
         <v>11</v>
       </c>
@@ -2422,7 +2428,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" ht="14.25" spans="1:13">
       <c r="A32" s="7" t="s">
         <v>11</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" ht="14.25" spans="1:15">
       <c r="A33" s="7" t="s">
         <v>11</v>
       </c>
@@ -2525,7 +2531,7 @@
       <c r="N34"/>
       <c r="O34"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" ht="14.25" spans="1:15">
       <c r="A35" s="7" t="s">
         <v>11</v>
       </c>
@@ -2558,7 +2564,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" ht="14.25" spans="1:15">
       <c r="A36" s="7" t="s">
         <v>11</v>
       </c>
@@ -2591,7 +2597,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" ht="14.25" spans="1:15">
       <c r="A37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2625,7 +2631,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" ht="14.25" spans="1:15">
       <c r="A38" s="7" t="s">
         <v>11</v>
       </c>
@@ -2659,7 +2665,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" ht="14.25" spans="1:15">
       <c r="A39" s="7" t="s">
         <v>11</v>
       </c>
@@ -2690,7 +2696,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" ht="14.25" spans="1:15">
       <c r="A40" s="7" t="s">
         <v>11</v>
       </c>
@@ -2758,7 +2764,7 @@
       <c r="N41"/>
       <c r="O41"/>
     </row>
-    <row r="42" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+    <row r="42" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A42" s="12" t="s">
         <v>71</v>
       </c>
@@ -2789,7 +2795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+    <row r="43" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
@@ -2818,7 +2824,7 @@
       <c r="J43" s="11"/>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" hidden="1" spans="1:15">
+    <row r="44" ht="14.25" spans="1:15">
       <c r="A44" s="8" t="s">
         <v>71</v>
       </c>
@@ -2849,7 +2855,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="1:15">
+    <row r="45" ht="14.25" spans="1:15">
       <c r="A45" s="8" t="s">
         <v>71</v>
       </c>
@@ -2880,7 +2886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:15">
+    <row r="46" ht="14.25" spans="1:15">
       <c r="A46" s="8" t="s">
         <v>71</v>
       </c>
@@ -2914,7 +2920,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:15">
+    <row r="47" ht="14.25" spans="1:15">
       <c r="A47" s="8" t="s">
         <v>71</v>
       </c>
@@ -2951,7 +2957,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="1:15">
+    <row r="48" ht="14.25" spans="1:15">
       <c r="A48" s="8" t="s">
         <v>71</v>
       </c>
@@ -2990,7 +2996,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:15">
+    <row r="49" ht="14.25" spans="1:15">
       <c r="A49" s="8" t="s">
         <v>71</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" hidden="1" spans="1:15">
+    <row r="50" ht="14.25" spans="1:15">
       <c r="A50" s="8" t="s">
         <v>71</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="1:15">
+    <row r="51" ht="14.25" spans="1:15">
       <c r="A51" s="8" t="s">
         <v>71</v>
       </c>
@@ -3102,7 +3108,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:15">
+    <row r="52" ht="14.25" spans="1:15">
       <c r="A52" s="8" t="s">
         <v>71</v>
       </c>
@@ -3136,7 +3142,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="1:15">
+    <row r="53" ht="14.25" spans="1:15">
       <c r="A53" s="8" t="s">
         <v>71</v>
       </c>
@@ -3175,7 +3181,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="1:15">
+    <row r="54" ht="14.25" spans="1:15">
       <c r="A54" s="8" t="s">
         <v>71</v>
       </c>
@@ -3209,7 +3215,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="1:15">
+    <row r="55" ht="14.25" spans="1:15">
       <c r="A55" s="8" t="s">
         <v>71</v>
       </c>
@@ -3243,7 +3249,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="1:15">
+    <row r="56" ht="14.25" spans="1:15">
       <c r="A56" s="8" t="s">
         <v>71</v>
       </c>
@@ -3279,7 +3285,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="1:15">
+    <row r="57" ht="14.25" spans="1:15">
       <c r="A57" s="8" t="s">
         <v>71</v>
       </c>
@@ -3315,7 +3321,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="58" hidden="1" spans="1:15">
+    <row r="58" ht="14.25" spans="1:15">
       <c r="A58" s="8" t="s">
         <v>71</v>
       </c>
@@ -3349,7 +3355,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="1:15">
+    <row r="59" ht="14.25" spans="1:15">
       <c r="A59" s="8" t="s">
         <v>71</v>
       </c>
@@ -3383,7 +3389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="1:15">
+    <row r="60" ht="14.25" spans="1:15">
       <c r="A60" s="8" t="s">
         <v>71</v>
       </c>
@@ -3419,7 +3425,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:15">
+    <row r="61" ht="14.25" spans="1:15">
       <c r="A61" s="27" t="s">
         <v>71</v>
       </c>
@@ -3447,7 +3453,7 @@
       </c>
       <c r="J61" s="23"/>
     </row>
-    <row r="62" hidden="1" spans="1:15">
+    <row r="62" ht="14.25" spans="1:15">
       <c r="A62" s="8" t="s">
         <v>71</v>
       </c>
@@ -3483,7 +3489,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="1:15">
+    <row r="63" ht="14.25" spans="1:15">
       <c r="A63" s="8" t="s">
         <v>71</v>
       </c>
@@ -3517,7 +3523,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="14.25" hidden="1" spans="1:15">
+    <row r="64" s="2" customFormat="1" ht="14.25" spans="1:15">
       <c r="A64" s="8" t="s">
         <v>71</v>
       </c>
@@ -3552,7 +3558,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" ht="14.25" hidden="1" spans="1:12">
+    <row r="65" ht="14.25" spans="1:12">
       <c r="A65" s="12" t="s">
         <v>71</v>
       </c>
@@ -3584,7 +3590,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" ht="14.25" hidden="1" spans="1:12">
+    <row r="66" ht="14.25" spans="1:12">
       <c r="A66" s="12" t="s">
         <v>71</v>
       </c>
@@ -3613,7 +3619,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:12">
+    <row r="67" ht="14.25" spans="1:12">
       <c r="A67" s="12" t="s">
         <v>71</v>
       </c>
@@ -3642,7 +3648,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" hidden="1" spans="1:12">
+    <row r="68" ht="14.25" spans="1:12">
       <c r="A68" s="12" t="s">
         <v>71</v>
       </c>
@@ -3671,7 +3677,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="1:12">
+    <row r="69" ht="14.25" spans="1:12">
       <c r="A69" s="12" t="s">
         <v>71</v>
       </c>
@@ -3700,7 +3706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="1:12">
+    <row r="70" ht="14.25" spans="1:12">
       <c r="A70" s="12" t="s">
         <v>71</v>
       </c>
@@ -3729,7 +3735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" ht="14.25" hidden="1" spans="1:12">
+    <row r="71" ht="14.25" spans="1:12">
       <c r="A71" s="12" t="s">
         <v>71</v>
       </c>
@@ -3758,14 +3764,61 @@
         <v>35</v>
       </c>
     </row>
+    <row r="72" ht="14.25" spans="1:12">
+      <c r="A72" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G72" s="3">
+        <v>8000</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25" spans="1:12">
+      <c r="A73" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="3">
+        <v>8005</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="10">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O71" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="B线"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A2:O71">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O73" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:O73">
       <sortCondition ref="G2"/>
     </sortState>
     <extLst/>

--- a/doc/6-3#装配线/点位信息.xlsx
+++ b/doc/6-3#装配线/点位信息.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\C2300040802\Desktop\NTP\doc\6-3#装配线\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="19635" windowHeight="7695"/>
   </bookViews>
@@ -1468,7 +1473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" ht="14.25" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>11</v>
       </c>
@@ -2782,7 +2787,7 @@
         <v>19</v>
       </c>
       <c r="G42" s="8">
-        <v>12484</v>
+        <v>12490</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>20</v>
@@ -3576,7 +3581,7 @@
         <v>19</v>
       </c>
       <c r="G65" s="3">
-        <v>12474</v>
+        <v>12470</v>
       </c>
       <c r="H65" s="21" t="s">
         <v>20</v>
